--- a/Config/__enums__.xlsx
+++ b/Config/__enums__.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G273"/>
+  <dimension ref="A1:G275"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="15.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32.06" customWidth="1" style="2" min="1" max="1"/>
@@ -657,68 +657,50 @@
       <c r="G15" s="4" t="n"/>
     </row>
     <row r="16" ht="26.25" customHeight="1" s="3">
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Protection</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>保护</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26.25" customHeight="1" s="3">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26.25" customHeight="1" s="3">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26.25" customHeight="1" s="3">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Mechanism</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>抵消机制（C# OffsetMechanism）</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Drain</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>流失（无源失命）</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n"/>
-      <c r="G17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="26.25" customHeight="1" s="3">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Discard</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>弃手牌</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="G18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="26.25" customHeight="1" s="3">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Mill</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>送墓（本组顶部）</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
@@ -729,12 +711,12 @@
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SendExtra</t>
+          <t>Discard</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>送额外组</t>
+          <t>弃手牌</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
@@ -743,20 +725,44 @@
     <row r="21" ht="26.25" customHeight="1" s="3">
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="4" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Mill</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>送墓（本组顶部）</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n"/>
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="26.25" customHeight="1" s="3">
       <c r="A22" s="4" t="n"/>
       <c r="B22" s="4" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SendExtra</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>送额外组</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n"/>
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="26.25" customHeight="1" s="3">
       <c r="A23" s="4" t="n"/>
       <c r="B23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
     </row>
     <row r="24" ht="26.25" customHeight="1" s="3">
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
     </row>
     <row r="25" ht="26.25" customHeight="1" s="3">
       <c r="A25" s="4" t="n"/>
@@ -1753,6 +1759,14 @@
     <row r="273">
       <c r="A273" s="4" t="n"/>
       <c r="B273" s="4" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="n"/>
+      <c r="B274" s="4" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="n"/>
+      <c r="B275" s="4" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/Config/__enums__.xlsx
+++ b/Config/__enums__.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G275"/>
+  <dimension ref="A1:G335"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="15.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32.06" customWidth="1" style="2" min="1" max="1"/>
@@ -1768,6 +1768,1326 @@
       <c r="A275" s="4" t="n"/>
       <c r="B275" s="4" t="n"/>
     </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>OnPlay</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>登场：经过发动区三关后进入战场之时（付费失败/被打落/被反制不进战场则不触发；横置非触发代价）</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>OnDeath</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>死亡时（亡语 / 进墓地时）</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>OnDraw</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>抽牌时</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>OnDealDamage</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>造成伤害时（payload 过滤：伤害源==自己）</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>OnTakeDamage</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>受到伤害时（payload 过滤：受伤者==自己）</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>OnTurnStart</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>回合开始时</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>OnTurnEnd</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>回合结束时</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>攻击宣言时（攻方）</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>OnAttacked</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>被攻击时（被指方，payload 过滤：攻击目标==自己）</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>OnSummon</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>进场时（任意来源含打出/效果召唤/复活/token/控制权变更——OnPlay 的超集）</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>OnMaterialDetach</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>超量素材取除时（暂无映射事件，待超量素材取除事件补齐）</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>OnTargeted</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>被指定为目标时（原子效果开始作用且目标含自己）</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>OnOtherCreatureEnter</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>其他生物进入战场时（payload 过滤：进场的不是自己）</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>OnSpellCast</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>施放法术时（使用宣言且打出的是法术）</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>OnTap</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>横置时</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>OnUntap</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>重置时</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>OnDestroy</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>破坏时（"破坏"死因）</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>OnExile</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>除外时</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>OnReturnFromGraveyard</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>从墓地回到战场时（进场事件的 Revived 来源）</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Activate_Active</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>激活式效果（主要阶段发动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Activate_Instant</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>瞬间发动</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>Activate_Response</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>响应式发动</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>OnLeaveBattlefield</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>离场时（战场 → 任何非战场区）</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>OnPhaseStart</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>阶段开始时</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>OnPhaseEnd</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>阶段结束时</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>OnBlockDeclare</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>阻拦宣言时</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>OnCardPlayed</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>使用卡牌时（使用宣言时点，付费前，含法术——与 OnPlay 登场分工）</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>OnGameStart</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>游戏开始时</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>OnAtomicEffectActivation</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>原子效果发动时</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>OnAtomicEffectStartApplying</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>原子效果开始作用时</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>TriggerTiming</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>触发时机（时点系统重排后全集）</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>OnAtomicEffectResolution</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>原子效果结算完成时</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>OwnLivingUnit</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>己方有生命单位（战场生物 + 己方角色）</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>EnemyLivingUnit</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>对方有生命单位（对方生物 + 对方角色）</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>OwnNonLivingUnit</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>己方无生命单位（战场结界等非生物持久物）</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>EnemyNonLivingUnit</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>对方无生命单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>OwnHand</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>己方手牌（卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>EnemyHand</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>对方手牌（卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>OwnDeck</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>己方牌库（卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>EnemyDeck</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>对方牌库（卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>OwnGraveyard</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>己方坟场（卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>EnemyGraveyard</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>对方坟场（卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>OwnExile</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>己方除外区（卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>EnemyExile</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>对方除外区（卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>OwnElementPool</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>己方元素池（地牌卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>EnemyElementPool</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>对方元素池（地牌卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>OwnActivation</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>己方发动区（被使用的卡——反制指向落点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>TargetKind</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>目标种类（M1 目标域模型）</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>EnemyActivation</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>对方发动区（被使用的卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>SelectionMode</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>组合层目标选择模式</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>无目标（DrawCard 等）：域为空集，不参与交集约束。</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>SelectionMode</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>组合层目标选择模式</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>自身：源卡在组合域内校验，取源卡为唯一目标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>SelectionMode</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>组合层目标选择模式</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>手动：TargetSelectionService 交互选取（TargetCount/DynamicTargetCount 管数量）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>SelectionMode</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>组合层目标选择模式</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>全域：候选全取（旧 All/AllAllies/AllEnemies/Random 的运行时行为）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>TargetFilter</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>域内属性过滤 token（逗号可组合；另支持 Power&gt;N/Life&lt;=N 比较式）</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>NoRole</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>仅生物（排除角色）</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>TargetFilter</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>域内属性过滤 token（逗号可组合；另支持 Power&gt;N/Life&lt;=N 比较式）</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Mortal</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>凡躯——滤除神佑持有者（效果死亡族守约）</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>TargetFilter</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>域内属性过滤 token（逗号可组合；另支持 Power&gt;N/Life&lt;=N 比较式）</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>仅指潜行中（2026-09-10 状态类定案：仅指持有该状态者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>TargetFilter</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>域内属性过滤 token（逗号可组合；另支持 Power&gt;N/Life&lt;=N 比较式）</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Untargetable</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>仅指免疫（辟邪）持有者</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>TargetFilter</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>域内属性过滤 token（逗号可组合；另支持 Power&gt;N/Life&lt;=N 比较式）</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Tapped</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>仅指已横置</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>TargetFilter</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>域内属性过滤 token（逗号可组合；另支持 Power&gt;N/Life&lt;=N 比较式）</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Untapped</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>仅指未横置</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>TargetFilter</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>域内属性过滤 token（逗号可组合；另支持 Power&gt;N/Life&lt;=N 比较式）</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Damaged</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>仅指已受伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>TargetFilter</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>域内属性过滤 token（逗号可组合；另支持 Power&gt;N/Life&lt;=N 比较式）</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Friendly</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>仅指己方</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>TargetFilter</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>域内属性过滤 token（逗号可组合；另支持 Power&gt;N/Life&lt;=N 比较式）</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>仅指敌方</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
